--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,98 +426,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ccegov-du</t>
+          <t>58t9c3c22997</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Frkiatto</t>
+          <t>Ccegov-du</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JTaniasdu</t>
+          <t>Hxervriadu</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jrezolrnadu</t>
+          <t>JTaniasdu</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>afluceat-du</t>
+          <t>Jrezolrnadu</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aisrtenc-</t>
+          <t>Jtaniasdu</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>anonyrezoias</t>
+          <t>Lrna2298rezo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>arezannrno</t>
+          <t>Tfcx87At</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ccegov-du</t>
+          <t>ainsa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cnavulro</t>
+          <t>arezannrno</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>culrezen</t>
+          <t>bcesllrn</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ecarezxosdu</t>
+          <t>ccegov-du</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fgirvuladu</t>
+          <t>ecarezxosdu</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fgonzalenavdu</t>
+          <t>ezenllenadu</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gbiallrndu</t>
+          <t>grezossodu</t>
         </is>
       </c>
     </row>
@@ -559,329 +559,224 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hxervriadu</t>
+          <t>invitado-deca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>invitado-deca</t>
+          <t>jlarezatat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jalbul-crndu</t>
+          <t>jrezolrnadu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jcalterondu</t>
+          <t>jsiaulena</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jlarezatat</t>
+          <t>jvulgas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jlucexenadu</t>
+          <t>lalbul-crndu</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jrezianozdu</t>
+          <t>lllazulretadu</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jrezolrnadu</t>
+          <t>lulaonadu</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jsiaulena</t>
+          <t>nrezulqirnadu</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jvulgas</t>
+          <t>oxulrsrdu</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lalbul-crndu</t>
+          <t>rezgakitr</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>lulaonadu</t>
+          <t>rezjzenzdu</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ncoaadu</t>
+          <t>rezsyczdu</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ngulro</t>
+          <t>rezt-zdu</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nolrve-du</t>
+          <t>reztoaesdu</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nrezulqirnadu</t>
+          <t>rgosurirno</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nxulesdu</t>
+          <t>rnvrtzar</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxulrsrdu</t>
+          <t>rzentovaldu</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rezgakitr</t>
+          <t>sstoccodu</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rezjxonce</t>
+          <t>trirta</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rezjzenzdu</t>
+          <t>txenaziattrdu</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rezle-</t>
+          <t>tzenllena</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rezleondu</t>
+          <t>tzenllenadu</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rezt-zdu</t>
+          <t>urez</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>reztoaesdu</t>
+          <t>vrezultrnenadu</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rezulaagadu</t>
+          <t>vvalvertedu</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rgosurirno</t>
+          <t>xab7749Tena</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rnvrtzar-ainsa</t>
+          <t>xabluce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rrezansiul</t>
+          <t>xaeedu</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rvrncr</t>
+          <t>xbenrtenadu</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rzentovaldu</t>
+          <t>xgalvandu</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sgf</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>sstoccodu</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>sxrntodu</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>trirta</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>tzenllenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>ulucecca</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>urez</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>vrezultrnenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>xabluce</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>xaee</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>xaeedu</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>xbenrtenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>xgalvandu</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>xgeezena</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>xnulvrnadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TOTAL: 65</t>
+          <t>TOTAL: 50</t>
         </is>
       </c>
     </row>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,370 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Usuario</t>
+          <t>MAC_Cliente</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>58t9c3c22997</t>
+          <t>28-5A-EB-2C-42-37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ccegov-du</t>
+          <t>90-73-5A-3C-38-94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hxervriadu</t>
+          <t>D0-77-14-7B-9E-CC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JTaniasdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jrezolrnadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jtaniasdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lrna2298rezo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tfcx87At</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ainsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>arezannrno</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>bcesllrn</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ccegov-du</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ecarezxosdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ezenllenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>frkiatto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>grezossodu</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>gt-zdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>gvrtarezegasdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>hcadardu</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>invitado-deca</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>jlarezatat</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>jrezolrnadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>jsiaulena</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>jvulgas</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>lalbul-crndu</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>lllazulretadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lulaonadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>nrezulqirnadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>oxulrsrdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rezgakitr</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rezjzenzdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rezsyczdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>rezt-zdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>reztoaesdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>rgosurirno</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>rnvrtzar</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>rzentovaldu</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sstoccodu</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>trirta</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>txenaziattrdu</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>tzenllena</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>tzenllenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>urez</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>vrezultrnenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>vvalvertedu</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>xab7749Tena</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>xabluce</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>xaeedu</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>xbenrtenadu</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>xgalvandu</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TOTAL: 50</t>
+          <t>TOTAL: 3</t>
         </is>
       </c>
     </row>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,11 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Usuario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>MAC_Cliente</t>
         </is>
@@ -438,28 +431,632 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-5A-EB-2C-42-37</t>
-        </is>
-      </c>
+          <t>abulbosadu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>90-73-5A-3C-38-94</t>
-        </is>
-      </c>
+          <t>afluceat-du</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D0-77-14-7B-9E-CC</t>
-        </is>
-      </c>
+          <t>ainsa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TOTAL: 3</t>
+          <t>alucdbultrdu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>anonyrezoias</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>arezannrno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>at-zdu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>azanrlletaresdu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cculadu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cjsalasdu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>clencrnasdu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cnavulrodu</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>creezerodu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>crkiagirnadu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>csienadu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>culrezen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cxrcrghetares</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ecarezxosdu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ejfiagazzkitodu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>erobsurdu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>evfernantenadu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ezenllenadu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ftalrezaiadu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>grezossodu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gt-zdu</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gtalqirncadu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>jasictadu</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>jcalterondu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>jcanale</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>jlarezatat</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>jlucexenadu</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>jrezvrlllesdu</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>jrezvrteladu</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>jsosadu</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>jsxrnetares</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>leult-du</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>lrezsurlcetarezsrezaodu</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ncoaadu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>nolrve-du</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>nrezulqirnadu</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>nrezvrcencrodu</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>rcriazdu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>resezoyanodu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>rezaxulrcrodu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>rezbsurbiag-du</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>rezftrcesuledu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>rezgatareze-nrdu</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>rezjxiagantetarezdu</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>rezjzenzdu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>rezliacerodu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>rezlianadu</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>rezsllavenadu</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>rezt-zdu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>reztoaedu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>reztoaesdu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>rezzentonrdu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>rgonzalenadu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>rgosurirno</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sfluceat-du</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sgf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sgrrezenenadu</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>steesngirnadu</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>tetarez-1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>tetarez-2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>tetarez-3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>tgt-zzentobuldu</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tgtarezavsrezu</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>treezerodu</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>tsictuletaresdu</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>txenaziattrdu</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tzenllenadu</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>vbec-du</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>vcrezeandu</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>vrezaondu</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>xabluce</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>xcatarezedu</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>xnulvrnadu</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>xoyanultdu</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TOTAL: 78</t>
         </is>
       </c>
     </row>
